--- a/samples/sample_recycling.xlsx
+++ b/samples/sample_recycling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Visual Studios Repos\Chaman\RPA_BOT\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5B8E5D-FAE0-44FB-B14C-DDEC9F03B39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFF40C3-1350-4172-9F6E-B82DF626489B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Finance Year</t>
   </si>
@@ -34,19 +34,16 @@
     <t>Quantity Processed (MT)</t>
   </si>
   <si>
-    <t>Quantity of Waste Generated (MT)</t>
-  </si>
-  <si>
     <t>Recycled Date</t>
   </si>
   <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
     <t>Domestically</t>
   </si>
   <si>
-    <t>Crumb Rubber</t>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Pyrolisis Oil (Batch)</t>
   </si>
 </sst>
 </file>
@@ -398,18 +395,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,28 +421,22 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>0.7</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46053</v>
+        <v>5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46183</v>
       </c>
     </row>
   </sheetData>
